--- a/CC_tuoi.xlsx
+++ b/CC_tuoi.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="14" uniqueCount="8">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="14" uniqueCount="9">
   <si>
     <t>Trai</t>
   </si>
@@ -29,7 +29,7 @@
       <rPr>
         <b/>
         <sz val="13"/>
-        <color theme="1"/>
+        <color rgb="FF000000"/>
         <rFont val="Arial"/>
         <family val="2"/>
       </rPr>
@@ -40,7 +40,7 @@
       <rPr>
         <b/>
         <sz val="13"/>
-        <color theme="1"/>
+        <color rgb="FF000000"/>
         <rFont val="Arial"/>
         <family val="2"/>
       </rPr>
@@ -55,7 +55,7 @@
       <rPr>
         <b/>
         <sz val="13"/>
-        <color theme="1"/>
+        <color rgb="FF000000"/>
         <rFont val="Arial"/>
         <family val="2"/>
       </rPr>
@@ -70,7 +70,7 @@
       <rPr>
         <b/>
         <sz val="13"/>
-        <color theme="1"/>
+        <color rgb="FF000000"/>
         <rFont val="Arial"/>
         <family val="2"/>
       </rPr>
@@ -85,7 +85,7 @@
       <rPr>
         <b/>
         <sz val="13"/>
-        <color theme="1"/>
+        <color rgb="FF000000"/>
         <rFont val="Arial"/>
         <family val="2"/>
       </rPr>
@@ -100,7 +100,7 @@
       <rPr>
         <b/>
         <sz val="13"/>
-        <color theme="1"/>
+        <color rgb="FF000000"/>
         <rFont val="Arial"/>
         <family val="2"/>
       </rPr>
@@ -115,11 +115,37 @@
       <rPr>
         <b/>
         <sz val="13"/>
-        <color theme="1"/>
+        <color rgb="FF000000"/>
         <rFont val="Arial"/>
         <family val="2"/>
       </rPr>
       <t>+3 SD</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t/>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="13"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">Tháng
+</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="13"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>tuổi</t>
     </r>
   </si>
 </sst>
@@ -130,7 +156,7 @@
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="#,##0.0"/>
   </numFmts>
-  <fonts count="5" x14ac:knownFonts="1">
+  <fonts count="4" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -141,20 +167,14 @@
     <font>
       <b/>
       <sz val="13"/>
-      <color theme="1"/>
+      <color rgb="FF000000"/>
       <name val="Arial"/>
       <family val="2"/>
     </font>
     <font>
       <sz val="11"/>
-      <color theme="1"/>
+      <color rgb="FF000000"/>
       <name val="Calibri"/>
-      <family val="2"/>
-    </font>
-    <font>
-      <sz val="13"/>
-      <color theme="1"/>
-      <name val="Arial"/>
       <family val="2"/>
     </font>
     <font>
@@ -328,16 +348,16 @@
     <xf xfId="0" numFmtId="1" applyNumberFormat="1" borderId="4" applyBorder="1" fontId="2" applyFont="1" fillId="0" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
-    <xf xfId="0" numFmtId="1" applyNumberFormat="1" borderId="4" applyBorder="1" fontId="4" applyFont="1" fillId="0" applyAlignment="1">
+    <xf xfId="0" numFmtId="1" applyNumberFormat="1" borderId="4" applyBorder="1" fontId="3" applyFont="1" fillId="0" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf xfId="0" numFmtId="164" applyNumberFormat="1" borderId="4" applyBorder="1" fontId="4" applyFont="1" fillId="0" applyAlignment="1">
+    <xf xfId="0" numFmtId="164" applyNumberFormat="1" borderId="4" applyBorder="1" fontId="3" applyFont="1" fillId="0" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf xfId="0" numFmtId="164" applyNumberFormat="1" borderId="4" applyBorder="1" fontId="4" applyFont="1" fillId="2" applyFill="1" applyAlignment="1">
+    <xf xfId="0" numFmtId="164" applyNumberFormat="1" borderId="4" applyBorder="1" fontId="3" applyFont="1" fillId="2" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf xfId="0" numFmtId="164" applyNumberFormat="1" borderId="4" applyBorder="1" fontId="4" applyFont="1" fillId="4" applyFill="1" applyAlignment="1">
+    <xf xfId="0" numFmtId="164" applyNumberFormat="1" borderId="4" applyBorder="1" fontId="3" applyFont="1" fillId="4" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf xfId="0" numFmtId="1" applyNumberFormat="1" borderId="0" fontId="0" fillId="0" applyAlignment="1">
@@ -709,7 +729,7 @@
       </c>
       <c r="G2" s="11"/>
       <c r="H2" s="12" t="s">
-        <v>2</v>
+        <v>8</v>
       </c>
       <c r="I2" s="13" t="s">
         <v>3</v>
